--- a/output/pdf_financials_xlsx/REI.UN.xlsx
+++ b/output/pdf_financials_xlsx/REI.UN.xlsx
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>619.457</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>647</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>266</v>
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>763.845</v>
+        <v>144.388</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>758</v>
+        <v>111</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>552</v>
@@ -1092,37 +1092,37 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>5.744</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>7.586</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>11.452</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>16.916</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>14.602</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>13.666</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>20.902</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>25.131</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>42.469</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>38.237</v>
       </c>
     </row>
     <row r="13">
@@ -2175,37 +2175,37 @@
         <v>713</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>418.856</v>
+        <v>413.486</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>679.301</v>
+        <v>673.557</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>707.9450000000001</v>
+        <v>700.359</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>525.922</v>
+        <v>514.47</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>777.199</v>
+        <v>760.283</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-54.15</v>
+        <v>-68.752</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>598.33</v>
+        <v>584.664</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>237.693</v>
+        <v>216.791</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>25.437</v>
+        <v>0.306</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>472.671</v>
+        <v>430.202</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>69.295</v>
+        <v>31.058</v>
       </c>
     </row>
     <row r="28">
@@ -2297,37 +2297,37 @@
         <v>717.0410000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>423.511</v>
+        <v>418.141</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>683.699</v>
+        <v>677.955</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>717.8099999999999</v>
+        <v>710.224</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>530.497</v>
+        <v>519.045</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>781.58</v>
+        <v>764.664</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-49.808</v>
+        <v>-64.41</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>602.352</v>
+        <v>588.686</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>242.467</v>
+        <v>221.565</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>28.069</v>
+        <v>2.938</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>474.121</v>
+        <v>431.652</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>70.80500000000001</v>
+        <v>32.568</v>
       </c>
     </row>
     <row r="30">
@@ -2364,37 +2364,37 @@
         <v>69.95501476581045</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>38.935090867637</v>
+        <v>38.44140489971831</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>60.32645332523921</v>
+        <v>59.81962919956376</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>62.13627026563794</v>
+        <v>61.4795982406799</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>46.21690093235829</v>
+        <v>45.21920264287245</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>58.92824156975101</v>
+        <v>57.65283772830942</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-4.355129089600696</v>
+        <v>-5.631903803830324</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>51.26133877305094</v>
+        <v>50.09833532046422</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>19.97508746983763</v>
+        <v>18.25312415815173</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>2.497528630954976</v>
+        <v>0.2614179029443771</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>38.25018595818079</v>
+        <v>34.82395689965358</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>4.928750475959768</v>
+        <v>2.267065115472886</v>
       </c>
     </row>
     <row r="31">
@@ -64584,7 +64584,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -68406,7 +68406,7 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
@@ -71692,7 +71692,7 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
@@ -89412,7 +89412,7 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E782" s="5" t="n">

--- a/output/pdf_financials_xlsx/REI.UN.xlsx
+++ b/output/pdf_financials_xlsx/REI.UN.xlsx
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>145.088</v>
+        <v>144.388</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>611</v>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>0.7</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-3</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>898</v>
@@ -1403,16 +1403,16 @@
         <v>3.85</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>7.341</v>
+        <v>0.32</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>1.44</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-2.064</v>
+        <v>0.699</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-10.905</v>
+        <v>0.275</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>0.059</v>
@@ -1713,16 +1713,16 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-275.129</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>147.687</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>7.021</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>0.741</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>145.088</v>
+        <v>144.388</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>611</v>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>145.088</v>
+        <v>144.388</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>611</v>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>18.99442949813116</v>
+        <v>18.90278786926667</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>15.03957783641161</v>
+        <v>15.43535620052771</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>68.88387824126269</v>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>0.4848048314264343</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>2.564102564102564</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>146.9721767594108</v>
@@ -2431,16 +2431,16 @@
         <v>0.5667590655688716</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1.036944960413591</v>
+        <v>0.04520125150965117</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>0.2738048607968482</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0.2655690498829772</v>
+        <v>0.08993835555629896</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-20.13850415512465</v>
+        <v>-0.5078485687903971</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>0.009860779168686176</v>
@@ -7659,10 +7659,10 @@
         <v>0</v>
       </c>
       <c r="P114" s="3" t="n">
-        <v>0</v>
+        <v>-19.241</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>0</v>
+        <v>-7.173</v>
       </c>
       <c r="R114" s="3" t="n">
         <v>0</v>
@@ -35340,7 +35340,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -35746,7 +35750,11 @@
           <t>Purchases of marketable securities</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -36368,7 +36376,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -36992,7 +37004,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -38862,7 +38878,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -41326,7 +41346,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -42888,7 +42912,11 @@
           <t>Deferred income taxes recovery</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -44454,7 +44482,11 @@
           <t>Deferred income taxes (recovery)</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -56734,7 +56766,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E468" t="inlineStr">
         <is>
           <t>-</t>
@@ -65624,7 +65660,11 @@
           <t>Current income tax recovery</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
           <t>-</t>
@@ -66208,7 +66248,11 @@
           <t>Current income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E560" t="inlineStr">
         <is>
           <t>-</t>
@@ -69416,7 +69460,11 @@
           <t>Net income from discontinued operations</t>
         </is>
       </c>
-      <c r="D591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E591" t="inlineStr">
         <is>
           <t>-</t>
@@ -70550,7 +70598,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D602" t="inlineStr"/>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E602" t="inlineStr">
         <is>
           <t>-</t>
@@ -70652,7 +70704,11 @@
           <t>Net income from discontinued operations 4</t>
         </is>
       </c>
-      <c r="D603" t="inlineStr"/>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E603" t="inlineStr">
         <is>
           <t>-</t>
@@ -73780,7 +73836,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
@@ -89726,7 +89782,11 @@
           <t>Future income tax recovery (Note 18)</t>
         </is>
       </c>
-      <c r="D785" t="inlineStr"/>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E785" t="inlineStr">
         <is>
           <t>-</t>
@@ -91512,7 +91572,11 @@
           <t>Future income tax recovery (Note 17)</t>
         </is>
       </c>
-      <c r="D802" t="inlineStr"/>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E802" s="5" t="n">
         <v>-0.7</v>
       </c>
